--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:W29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,61 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Отправлены вехи</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tg_username</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>employee_id</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>raw_input</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>feedback_q1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>feedback_q2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>feedback_q3</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>question</t>
         </is>
       </c>
     </row>
@@ -521,6 +576,17 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -553,6 +619,17 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -585,6 +662,17 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -617,6 +705,17 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -649,6 +748,17 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -681,6 +791,17 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -713,6 +834,17 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -761,6 +893,17 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -809,6 +952,17 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -863,6 +1017,17 @@
           <t>nan,first_week</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -917,6 +1082,17 @@
           <t>nan,first_week</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -971,6 +1147,17 @@
           <t>nan,first_week</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1025,6 +1212,17 @@
           <t>nan,first_week</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1079,6 +1277,17 @@
           <t>nan,first_week</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1133,6 +1342,17 @@
           <t>nan,first_week</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1187,6 +1407,17 @@
           <t>nan,first_week</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1241,6 +1472,17 @@
           <t>nan,first_week</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1293,6 +1535,607 @@
       <c r="L19" t="inlineStr">
         <is>
           <t>nan,first_week</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-26 10:23:08</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Не указан</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Кее</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>12.09.2025</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>785314750</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Кее | 122 | 12.09.2025</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Кен</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Кее</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Уке</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-26 10:47:37</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Не указан</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Кен</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>123</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>12.09.2025</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>785314750</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Кен | 123 | 12.09.2025</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Кен</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Кее</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Уке</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-26 10:59:01</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Не указан</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Кен</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>223</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>12.09.2025</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>785314750</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Кен | 223 | 12.09.2025</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Кен</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Кее</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Уке</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-26 11:18:11</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Не указан</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Кее</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>123</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>12.09.2025</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>785314750</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Кее | 123 | 12.09.2025</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Кен</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Кее</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Уке</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2025-11-26 11:27:16</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Не указан</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Кен</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Уке</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>12.09.2025</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>785314750</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Кен | Уке | 12.09.2025</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2025-11-26 11:29:29</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Не указан</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Ке</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>12.09.2025</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>785314750</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Ке | 123 | 12.09.2025</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2025-11-26 11:32:06</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Не указан</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Ппр</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>12.09.2025</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>785314750</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Ппр | 233 | 12.09.2025</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2025-11-26 11:36:18</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Не указан</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Кен</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>12.09.2025</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>785314750</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Кен | 233 | 12.09.2025</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2025-11-26 11:38:04</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Не указан</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Кен</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>12.09.2025</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>785314750</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Кен | 123 | 12.09.2025</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2025-11-26 11:39:24</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Не указан</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Кен</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>12.09.2025</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>785314750</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Кен | 123 | 12.09.2025</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>?</t>
         </is>
       </c>
     </row>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,6 +2139,57 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2025-12-04 22:29:00</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X0re4ik</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>09.09.2024</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>511246625</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>4 | 4 | 09.09.2024</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
